--- a/src/test/resources/testData/SampleDataFile.xlsx
+++ b/src/test/resources/testData/SampleDataFile.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\IdeaProjects\java\ExcelDataReader\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D46F439-A3F0-4426-A4D7-3929899F3A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B2D862-CEF8-4522-81FD-A52ED615E8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="35">
   <si>
     <t>Test</t>
   </si>
@@ -130,6 +130,18 @@
   </si>
   <si>
     <t>listOfComposites</t>
+  </si>
+  <si>
+    <t>Sample string value</t>
+  </si>
+  <si>
+    <t>THREE</t>
+  </si>
+  <si>
+    <t>String two</t>
+  </si>
+  <si>
+    <t>string one</t>
   </si>
 </sst>
 </file>
@@ -189,7 +201,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -233,6 +245,41 @@
         <color indexed="64"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -242,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -267,6 +314,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -276,10 +333,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -570,7 +630,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -588,13 +648,13 @@
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="12"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="13"/>
+      <c r="A2" s="19"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -724,7 +784,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -762,7 +822,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="14"/>
+      <c r="A2" s="20"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
@@ -852,39 +912,40 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9931B40-81B7-4228-B503-3D435B06AB8F}">
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AI9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="4.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.06640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.46484375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.9296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.1328125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="6.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.3984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.06640625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="8.265625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.9296875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.53125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8.86328125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="16.1328125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6.59765625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="12" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.3984375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="11.06640625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="7.53125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.265625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="8.265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.796875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="10.19921875" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="8.46484375" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="8.86328125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="9.9296875" bestFit="1" customWidth="1"/>
@@ -892,7 +953,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -928,109 +989,505 @@
       <c r="L1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y1" s="12" t="s">
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-      <c r="AH1" s="12"/>
-      <c r="AI1" s="12"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="23"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="14"/>
-      <c r="M2" s="16" t="s">
+      <c r="A2" s="20"/>
+      <c r="N2" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="O2" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="P2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="Q2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="16" t="s">
+      <c r="R2" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="16" t="s">
+      <c r="S2" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="16" t="s">
+      <c r="T2" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="T2" s="16" t="s">
+      <c r="U2" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="U2" s="16" t="s">
+      <c r="V2" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="V2" s="16" t="s">
+      <c r="W2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="W2" s="16" t="s">
+      <c r="X2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="15" t="s">
+      <c r="Y2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="Z2" s="15" t="s">
+      <c r="Z2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AA2" s="15" t="s">
+      <c r="AA2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="15" t="s">
+      <c r="AB2" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" s="15" t="s">
+      <c r="AC2" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" s="15" t="s">
+      <c r="AD2" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="AE2" s="15" t="s">
+      <c r="AE2" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="AF2" s="15" t="s">
+      <c r="AF2" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="AG2" s="15" t="s">
+      <c r="AG2" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="AH2" s="15" t="s">
+      <c r="AH2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="AI2" s="15" t="s">
+      <c r="AI2" s="13" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="E3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="F3" s="2">
+        <v>123</v>
+      </c>
+      <c r="G3" s="8">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="H3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="I3" s="10">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="J3" s="2">
+        <v>123000</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="R3" s="2">
+        <v>123</v>
+      </c>
+      <c r="S3" s="8">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="T3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="U3" s="10">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="V3" s="2">
+        <v>123000</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AB3" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC3" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD3" s="8">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE3" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF3" s="10">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG3" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="M4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AB4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC4" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF4" s="10">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG4" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI4" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="Y5" s="14">
+        <v>123.56</v>
+      </c>
+      <c r="Z5" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="15">
+        <v>45424</v>
+      </c>
+      <c r="AB5" s="14">
+        <v>123.56</v>
+      </c>
+      <c r="AC5" s="14">
+        <v>123</v>
+      </c>
+      <c r="AD5" s="16">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE5" s="15">
+        <v>45424</v>
+      </c>
+      <c r="AF5" s="17">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG5" s="14">
+        <v>123000</v>
+      </c>
+      <c r="AH5" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI5" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="Y6" s="14"/>
+      <c r="Z6" s="14"/>
+      <c r="AA6" s="15"/>
+      <c r="AB6" s="14"/>
+      <c r="AC6" s="14"/>
+      <c r="AD6" s="16"/>
+      <c r="AE6" s="15"/>
+      <c r="AF6" s="17"/>
+      <c r="AG6" s="14"/>
+      <c r="AH6" s="14"/>
+      <c r="AI6" s="14"/>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="E7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="F7" s="2">
+        <v>123</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="H7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="J7" s="2">
+        <v>123000</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="R7" s="2">
+        <v>123</v>
+      </c>
+      <c r="S7" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="T7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="U7" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="V7" s="2">
+        <v>123000</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AB7" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC7" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD7" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE7" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AF7" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG7" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AB8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC8" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD8" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AF8" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG8" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="Y9" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA9" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AB9" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC9" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD9" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE9" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AF9" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG9" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="M1:W1"/>
+    <mergeCell ref="N1:X1"/>
     <mergeCell ref="Y1:AI1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/test/resources/testData/SampleDataFile.xlsx
+++ b/src/test/resources/testData/SampleDataFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\IdeaProjects\java\ExcelDataReader\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B2D862-CEF8-4522-81FD-A52ED615E8AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C1414BE-CDCF-49FE-91C7-2F0DAC346606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/src/test/resources/testData/SampleDataFile.xlsx
+++ b/src/test/resources/testData/SampleDataFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\IdeaProjects\java\ExcelDataReader\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0C1414BE-CDCF-49FE-91C7-2F0DAC346606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEC463D-2F35-4BFA-851C-0D6AA8DB937B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="36">
   <si>
     <t>Test</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t>string one</t>
+  </si>
+  <si>
+    <t>comments</t>
   </si>
 </sst>
 </file>
@@ -201,7 +204,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -285,11 +288,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -341,6 +357,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -912,7 +934,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9931B40-81B7-4228-B503-3D435B06AB8F}">
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
@@ -953,7 +975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1020,7 +1042,7 @@
       <c r="AI1" s="23"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="20"/>
+      <c r="A2" s="24"/>
       <c r="N2" s="12" t="s">
         <v>15</v>
       </c>
@@ -1089,115 +1111,105 @@
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="12"/>
+      <c r="P3" s="12"/>
+      <c r="Q3" s="12"/>
+      <c r="R3" s="12"/>
+      <c r="S3" s="12"/>
+      <c r="T3" s="12"/>
+      <c r="U3" s="12"/>
+      <c r="V3" s="12"/>
+      <c r="W3" s="12"/>
+      <c r="X3" s="12"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+      <c r="AF3" s="13"/>
+      <c r="AG3" s="13"/>
+      <c r="AH3" s="13"/>
+      <c r="AI3" s="13"/>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="E3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="D4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="E4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="F4" s="2">
         <v>123</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G4" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="H3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="I3" s="10">
+      <c r="H4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="I4" s="10">
         <v>0.54873842592592592</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J4" s="2">
         <v>123000</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="O3" s="2" t="s">
+      <c r="N4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="R3" s="2">
+      <c r="P4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="R4" s="2">
         <v>123</v>
       </c>
-      <c r="S3" s="8">
+      <c r="S4" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="T3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="U3" s="10">
+      <c r="T4" s="9">
+        <v>45424</v>
+      </c>
+      <c r="U4" s="10">
         <v>0.54873842592592592</v>
       </c>
-      <c r="V3" s="2">
+      <c r="V4" s="2">
         <v>123000</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="AB3" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="AC3" s="2">
-        <v>123</v>
-      </c>
-      <c r="AD3" s="8">
-        <v>45424.548738425925</v>
-      </c>
-      <c r="AE3" s="9">
-        <v>45424</v>
-      </c>
-      <c r="AF3" s="10">
-        <v>0.54873842592592592</v>
-      </c>
-      <c r="AG3" s="2">
-        <v>123000</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="M4" t="s">
-        <v>33</v>
       </c>
       <c r="Y4" s="2">
         <v>123.56</v>
@@ -1230,191 +1242,168 @@
         <v>31</v>
       </c>
       <c r="AI4" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="M5" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AB5" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC5" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD5" s="8">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE5" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF5" s="10">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG5" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI5" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="Y5" s="14">
-        <v>123.56</v>
-      </c>
-      <c r="Z5" s="14" t="s">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="Y6" s="14">
+        <v>123.56</v>
+      </c>
+      <c r="Z6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="AA5" s="15">
-        <v>45424</v>
-      </c>
-      <c r="AB5" s="14">
-        <v>123.56</v>
-      </c>
-      <c r="AC5" s="14">
+      <c r="AA6" s="15">
+        <v>45424</v>
+      </c>
+      <c r="AB6" s="14">
+        <v>123.56</v>
+      </c>
+      <c r="AC6" s="14">
         <v>123</v>
       </c>
-      <c r="AD5" s="16">
+      <c r="AD6" s="16">
         <v>45424.548738425925</v>
       </c>
-      <c r="AE5" s="15">
-        <v>45424</v>
-      </c>
-      <c r="AF5" s="17">
+      <c r="AE6" s="15">
+        <v>45424</v>
+      </c>
+      <c r="AF6" s="17">
         <v>0.54873842592592592</v>
       </c>
-      <c r="AG5" s="14">
+      <c r="AG6" s="14">
         <v>123000</v>
       </c>
-      <c r="AH5" s="14" t="s">
+      <c r="AH6" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="AI5" s="14" t="s">
+      <c r="AI6" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="Y6" s="14"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="15"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="16"/>
-      <c r="AE6" s="15"/>
-      <c r="AF6" s="17"/>
-      <c r="AG6" s="14"/>
-      <c r="AH6" s="14"/>
-      <c r="AI6" s="14"/>
-    </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A7" s="2" t="s">
+      <c r="Y7" s="14"/>
+      <c r="Z7" s="14"/>
+      <c r="AA7" s="15"/>
+      <c r="AB7" s="14"/>
+      <c r="AC7" s="14"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="15"/>
+      <c r="AF7" s="17"/>
+      <c r="AG7" s="14"/>
+      <c r="AH7" s="14"/>
+      <c r="AI7" s="14"/>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="E7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="D8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="E8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="F8" s="2">
         <v>123</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G8" s="2">
         <v>45424.548738425925</v>
       </c>
-      <c r="H7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="H8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="I8" s="2">
         <v>0.54873842592592592</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J8" s="2">
         <v>123000</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="N7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="O7" s="2" t="s">
+      <c r="N8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="R7" s="2">
+      <c r="P8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="R8" s="2">
         <v>123</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S8" s="2">
         <v>45424.548738425925</v>
       </c>
-      <c r="T7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="U7" s="2">
+      <c r="T8" s="2">
+        <v>45424</v>
+      </c>
+      <c r="U8" s="2">
         <v>0.54873842592592592</v>
       </c>
-      <c r="V7" s="2">
+      <c r="V8" s="2">
         <v>123000</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="X7" s="2" t="s">
+      <c r="X8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Y7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="AB7" s="2">
-        <v>123.56</v>
-      </c>
-      <c r="AC7" s="2">
-        <v>123</v>
-      </c>
-      <c r="AD7" s="2">
-        <v>45424.548738425925</v>
-      </c>
-      <c r="AE7" s="2">
-        <v>45424</v>
-      </c>
-      <c r="AF7" s="2">
-        <v>0.54873842592592592</v>
-      </c>
-      <c r="AG7" s="2">
-        <v>123000</v>
-      </c>
-      <c r="AH7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
       <c r="Y8" s="2">
         <v>123.56</v>
       </c>
@@ -1446,10 +1435,36 @@
         <v>31</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
       <c r="Y9" s="2">
         <v>123.56</v>
       </c>
@@ -1481,14 +1496,49 @@
         <v>31</v>
       </c>
       <c r="AI9" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.45">
+      <c r="Y10" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="Z10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA10" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AB10" s="2">
+        <v>123.56</v>
+      </c>
+      <c r="AC10" s="2">
+        <v>123</v>
+      </c>
+      <c r="AD10" s="2">
+        <v>45424.548738425925</v>
+      </c>
+      <c r="AE10" s="2">
+        <v>45424</v>
+      </c>
+      <c r="AF10" s="2">
+        <v>0.54873842592592592</v>
+      </c>
+      <c r="AG10" s="2">
+        <v>123000</v>
+      </c>
+      <c r="AH10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AI10" s="2" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:A2"/>
     <mergeCell ref="N1:X1"/>
     <mergeCell ref="Y1:AI1"/>
+    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testData/SampleDataFile.xlsx
+++ b/src/test/resources/testData/SampleDataFile.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\IdeaProjects\java\ExcelDataReader\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FEC463D-2F35-4BFA-851C-0D6AA8DB937B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0918FB-6310-48AF-84FD-C24CB599AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -330,12 +330,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -363,6 +357,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +652,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -670,13 +670,13 @@
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="18"/>
+      <c r="H1" s="16"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="19"/>
+      <c r="A2" s="17"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -806,7 +806,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -844,7 +844,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="20"/>
+      <c r="A2" s="18"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
@@ -975,7 +975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1014,129 +1014,129 @@
       <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="N1" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="18"/>
-      <c r="P1" s="18"/>
-      <c r="Q1" s="18"/>
-      <c r="R1" s="18"/>
-      <c r="S1" s="18"/>
-      <c r="T1" s="18"/>
-      <c r="U1" s="18"/>
-      <c r="V1" s="18"/>
-      <c r="W1" s="18"/>
-      <c r="X1" s="18"/>
-      <c r="Y1" s="21" t="s">
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16"/>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="16"/>
+      <c r="Y1" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="22"/>
-      <c r="AA1" s="22"/>
-      <c r="AB1" s="22"/>
-      <c r="AC1" s="22"/>
-      <c r="AD1" s="22"/>
-      <c r="AE1" s="22"/>
-      <c r="AF1" s="22"/>
-      <c r="AG1" s="22"/>
-      <c r="AH1" s="22"/>
-      <c r="AI1" s="23"/>
+      <c r="Z1" s="20"/>
+      <c r="AA1" s="20"/>
+      <c r="AB1" s="20"/>
+      <c r="AC1" s="20"/>
+      <c r="AD1" s="20"/>
+      <c r="AE1" s="20"/>
+      <c r="AF1" s="20"/>
+      <c r="AG1" s="20"/>
+      <c r="AH1" s="20"/>
+      <c r="AI1" s="21"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="24"/>
-      <c r="N2" s="12" t="s">
+      <c r="A2" s="22"/>
+      <c r="N2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="12" t="s">
+      <c r="O2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="12" t="s">
+      <c r="P2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="12" t="s">
+      <c r="Q2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="12" t="s">
+      <c r="R2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="12" t="s">
+      <c r="S2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="12" t="s">
+      <c r="T2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="12" t="s">
+      <c r="U2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="12" t="s">
+      <c r="V2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="12" t="s">
+      <c r="W2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="X2" s="12" t="s">
+      <c r="X2" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="13" t="s">
+      <c r="Y2" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="Z2" s="13" t="s">
+      <c r="Z2" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AA2" s="13" t="s">
+      <c r="AA2" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="13" t="s">
+      <c r="AB2" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" s="13" t="s">
+      <c r="AC2" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" s="13" t="s">
+      <c r="AD2" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="AE2" s="13" t="s">
+      <c r="AE2" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="AF2" s="13" t="s">
+      <c r="AF2" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="AG2" s="13" t="s">
+      <c r="AG2" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="AH2" s="13" t="s">
+      <c r="AH2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="AI2" s="13" t="s">
+      <c r="AI2" s="25" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="25"/>
+      <c r="A3" s="23"/>
       <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="12"/>
-      <c r="P3" s="12"/>
-      <c r="Q3" s="12"/>
-      <c r="R3" s="12"/>
-      <c r="S3" s="12"/>
-      <c r="T3" s="12"/>
-      <c r="U3" s="12"/>
-      <c r="V3" s="12"/>
-      <c r="W3" s="12"/>
-      <c r="X3" s="12"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="13"/>
-      <c r="AA3" s="13"/>
-      <c r="AB3" s="13"/>
-      <c r="AC3" s="13"/>
-      <c r="AD3" s="13"/>
-      <c r="AE3" s="13"/>
-      <c r="AF3" s="13"/>
-      <c r="AG3" s="13"/>
-      <c r="AH3" s="13"/>
-      <c r="AI3" s="13"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
+      <c r="AH3" s="24"/>
+      <c r="AI3" s="24"/>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -1284,52 +1284,52 @@
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="Y6" s="14">
-        <v>123.56</v>
-      </c>
-      <c r="Z6" s="14" t="s">
+      <c r="Y6" s="12">
+        <v>123.56</v>
+      </c>
+      <c r="Z6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="AA6" s="15">
-        <v>45424</v>
-      </c>
-      <c r="AB6" s="14">
-        <v>123.56</v>
-      </c>
-      <c r="AC6" s="14">
+      <c r="AA6" s="13">
+        <v>45424</v>
+      </c>
+      <c r="AB6" s="12">
+        <v>123.56</v>
+      </c>
+      <c r="AC6" s="12">
         <v>123</v>
       </c>
-      <c r="AD6" s="16">
+      <c r="AD6" s="14">
         <v>45424.548738425925</v>
       </c>
-      <c r="AE6" s="15">
-        <v>45424</v>
-      </c>
-      <c r="AF6" s="17">
+      <c r="AE6" s="13">
+        <v>45424</v>
+      </c>
+      <c r="AF6" s="15">
         <v>0.54873842592592592</v>
       </c>
-      <c r="AG6" s="14">
+      <c r="AG6" s="12">
         <v>123000</v>
       </c>
-      <c r="AH6" s="14" t="s">
+      <c r="AH6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="AI6" s="14" t="s">
+      <c r="AI6" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="Y7" s="14"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="15"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="16"/>
-      <c r="AE7" s="15"/>
-      <c r="AF7" s="17"/>
-      <c r="AG7" s="14"/>
-      <c r="AH7" s="14"/>
-      <c r="AI7" s="14"/>
+      <c r="Y7" s="12"/>
+      <c r="Z7" s="12"/>
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="12"/>
+      <c r="AC7" s="12"/>
+      <c r="AD7" s="14"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="15"/>
+      <c r="AG7" s="12"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="12"/>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">

--- a/src/test/resources/testData/SampleDataFile.xlsx
+++ b/src/test/resources/testData/SampleDataFile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frede\IdeaProjects\java\ExcelDataReader\src\test\resources\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE0918FB-6310-48AF-84FD-C24CB599AFED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86522977-AF22-442A-BB47-B7B00BE51130}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SampleDataRecord" sheetId="1" r:id="rId1"/>
@@ -334,6 +334,12 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -357,12 +363,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -652,7 +652,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -670,13 +670,13 @@
       <c r="F1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="16"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" s="17"/>
+      <c r="A2" s="19"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -806,7 +806,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -844,7 +844,7 @@
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" s="18"/>
+      <c r="A2" s="20"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" s="11" t="s">
@@ -975,7 +975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -1014,129 +1014,129 @@
       <c r="M1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="N1" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
-      <c r="Y1" s="19" t="s">
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+      <c r="U1" s="18"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="20"/>
-      <c r="AA1" s="20"/>
-      <c r="AB1" s="20"/>
-      <c r="AC1" s="20"/>
-      <c r="AD1" s="20"/>
-      <c r="AE1" s="20"/>
-      <c r="AF1" s="20"/>
-      <c r="AG1" s="20"/>
-      <c r="AH1" s="20"/>
-      <c r="AI1" s="21"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+      <c r="AH1" s="22"/>
+      <c r="AI1" s="23"/>
     </row>
     <row r="2" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A2" s="22"/>
-      <c r="N2" s="25" t="s">
+      <c r="A2" s="24"/>
+      <c r="N2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="O2" s="25" t="s">
+      <c r="O2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="25" t="s">
+      <c r="P2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="25" t="s">
+      <c r="Q2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="25" t="s">
+      <c r="R2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="25" t="s">
+      <c r="S2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="T2" s="25" t="s">
+      <c r="T2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="25" t="s">
+      <c r="U2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="V2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="W2" s="25" t="s">
+      <c r="W2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="X2" s="25" t="s">
+      <c r="X2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="Y2" s="25" t="s">
+      <c r="Y2" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Z2" s="25" t="s">
+      <c r="Z2" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="AA2" s="25" t="s">
+      <c r="AA2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="AB2" s="25" t="s">
+      <c r="AB2" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="AC2" s="25" t="s">
+      <c r="AC2" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="AD2" s="25" t="s">
+      <c r="AD2" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="AE2" s="25" t="s">
+      <c r="AE2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="AF2" s="25" t="s">
+      <c r="AF2" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="AG2" s="25" t="s">
+      <c r="AG2" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="AH2" s="25" t="s">
+      <c r="AH2" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AI2" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.45">
-      <c r="A3" s="23"/>
+      <c r="A3" s="25"/>
       <c r="B3" t="s">
         <v>35</v>
       </c>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="24"/>
-      <c r="Q3" s="24"/>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="24"/>
-      <c r="W3" s="24"/>
-      <c r="X3" s="24"/>
-      <c r="Y3" s="24"/>
-      <c r="Z3" s="24"/>
-      <c r="AA3" s="24"/>
-      <c r="AB3" s="24"/>
-      <c r="AC3" s="24"/>
-      <c r="AD3" s="24"/>
-      <c r="AE3" s="24"/>
-      <c r="AF3" s="24"/>
-      <c r="AG3" s="24"/>
-      <c r="AH3" s="24"/>
-      <c r="AI3" s="24"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="16"/>
+      <c r="P3" s="16"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="16"/>
+      <c r="X3" s="16"/>
+      <c r="Y3" s="16"/>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="16"/>
+      <c r="AC3" s="16"/>
+      <c r="AD3" s="16"/>
+      <c r="AE3" s="16"/>
+      <c r="AF3" s="16"/>
+      <c r="AG3" s="16"/>
+      <c r="AH3" s="16"/>
+      <c r="AI3" s="16"/>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
@@ -1341,7 +1341,7 @@
       <c r="C8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="9">
         <v>45424</v>
       </c>
       <c r="E8" s="2">
@@ -1350,13 +1350,13 @@
       <c r="F8" s="2">
         <v>123</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="H8" s="2">
-        <v>45424</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H8" s="9">
+        <v>45424</v>
+      </c>
+      <c r="I8" s="10">
         <v>0.54873842592592592</v>
       </c>
       <c r="J8" s="2">
@@ -1377,7 +1377,7 @@
       <c r="O8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="9">
         <v>45424</v>
       </c>
       <c r="Q8" s="2">
@@ -1386,13 +1386,13 @@
       <c r="R8" s="2">
         <v>123</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="T8" s="2">
-        <v>45424</v>
-      </c>
-      <c r="U8" s="2">
+      <c r="T8" s="9">
+        <v>45424</v>
+      </c>
+      <c r="U8" s="10">
         <v>0.54873842592592592</v>
       </c>
       <c r="V8" s="2">
@@ -1410,7 +1410,7 @@
       <c r="Z8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="9">
         <v>45424</v>
       </c>
       <c r="AB8" s="2">
@@ -1419,13 +1419,13 @@
       <c r="AC8" s="2">
         <v>123</v>
       </c>
-      <c r="AD8" s="2">
+      <c r="AD8" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="AE8" s="2">
-        <v>45424</v>
-      </c>
-      <c r="AF8" s="2">
+      <c r="AE8" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF8" s="10">
         <v>0.54873842592592592</v>
       </c>
       <c r="AG8" s="2">
@@ -1471,7 +1471,7 @@
       <c r="Z9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="9">
         <v>45424</v>
       </c>
       <c r="AB9" s="2">
@@ -1480,13 +1480,13 @@
       <c r="AC9" s="2">
         <v>123</v>
       </c>
-      <c r="AD9" s="2">
+      <c r="AD9" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="AE9" s="2">
-        <v>45424</v>
-      </c>
-      <c r="AF9" s="2">
+      <c r="AE9" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF9" s="10">
         <v>0.54873842592592592</v>
       </c>
       <c r="AG9" s="2">
@@ -1506,7 +1506,7 @@
       <c r="Z10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="AA10" s="2">
+      <c r="AA10" s="9">
         <v>45424</v>
       </c>
       <c r="AB10" s="2">
@@ -1515,13 +1515,13 @@
       <c r="AC10" s="2">
         <v>123</v>
       </c>
-      <c r="AD10" s="2">
+      <c r="AD10" s="8">
         <v>45424.548738425925</v>
       </c>
-      <c r="AE10" s="2">
-        <v>45424</v>
-      </c>
-      <c r="AF10" s="2">
+      <c r="AE10" s="9">
+        <v>45424</v>
+      </c>
+      <c r="AF10" s="10">
         <v>0.54873842592592592</v>
       </c>
       <c r="AG10" s="2">
